--- a/AAII_Financials/Yearly/PXED_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PXED_YR_FIN.xlsx
@@ -2507,10 +2507,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>6500</v>
+        <v>3700</v>
       </c>
       <c r="E83" s="3">
-        <v>4800</v>
+        <v>4400</v>
       </c>
       <c r="F83" s="3">
         <v>3300</v>
